--- a/.claude/skills/testcase-generator/outputs/excel_exports/business_site/data_analysis_p_control_chart_testcases.xlsx
+++ b/.claude/skills/testcase-generator/outputs/excel_exports/business_site/data_analysis_p_control_chart_testcases.xlsx
@@ -77,7 +77,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P70"/>
+  <dimension ref="A1:P71"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -237,7 +237,7 @@
       </c>
       <c r="K2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L2" t="inlineStr" s="2">
@@ -324,7 +324,7 @@
       </c>
       <c r="K3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、监控项目用例模板</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
         </is>
       </c>
       <c r="L3" t="inlineStr" s="2">
@@ -409,7 +409,7 @@
       </c>
       <c r="K4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L4" t="inlineStr" s="2">
@@ -494,7 +494,7 @@
       </c>
       <c r="K5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、数据分析核心流程</t>
+          <t xml:space="preserve">来源：prd、data_analysis_flow.md</t>
         </is>
       </c>
       <c r="L5" t="inlineStr" s="2">
@@ -584,7 +584,7 @@
       </c>
       <c r="K6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、UI设计图</t>
+          <t xml:space="preserve">来源：prd、UI图</t>
         </is>
       </c>
       <c r="L6" t="inlineStr" s="2">
@@ -670,7 +670,7 @@
       </c>
       <c r="K7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L7" t="inlineStr" s="2">
@@ -756,7 +756,7 @@
       </c>
       <c r="K8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、监控项目用例模板</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
         </is>
       </c>
       <c r="L8" t="inlineStr" s="2">
@@ -842,7 +842,7 @@
       </c>
       <c r="K9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、监控项目用例模板</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
         </is>
       </c>
       <c r="L9" t="inlineStr" s="2">
@@ -928,7 +928,7 @@
       </c>
       <c r="K10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、监控项目用例模板</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
         </is>
       </c>
       <c r="L10" t="inlineStr" s="2">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="K11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、监控项目用例模板</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
         </is>
       </c>
       <c r="L11" t="inlineStr" s="2">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="K12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、监控项目用例模板</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
         </is>
       </c>
       <c r="L12" t="inlineStr" s="2">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="K13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L13" t="inlineStr" s="2">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="K14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L14" t="inlineStr" s="2">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="K15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L15" t="inlineStr" s="2">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="K16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L16" t="inlineStr" s="2">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="K17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L17" t="inlineStr" s="2">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="K18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L18" t="inlineStr" s="2">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="K19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L19" t="inlineStr" s="2">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="K20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L20" t="inlineStr" s="2">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="K21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L21" t="inlineStr" s="2">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="K22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L22" t="inlineStr" s="2">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="K23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L23" t="inlineStr" s="2">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="K24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、coverage_dimension_rules.md-小数位数默认选项</t>
+          <t xml:space="preserve">来源：prd、coverage_dimension_rules.md-小数位数默认选项</t>
         </is>
       </c>
       <c r="L24" t="inlineStr" s="2">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="K25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、监控项目用例模板</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
         </is>
       </c>
       <c r="L25" t="inlineStr" s="2">
@@ -2312,7 +2312,7 @@
       </c>
       <c r="K26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、UI设计图</t>
+          <t xml:space="preserve">来源：prd、UI图</t>
         </is>
       </c>
       <c r="L26" t="inlineStr" s="2">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="K27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、监控项目用例模板</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
         </is>
       </c>
       <c r="L27" t="inlineStr" s="2">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="K28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、监控项目用例模板</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
         </is>
       </c>
       <c r="L28" t="inlineStr" s="2">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="K29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、监控项目用例模板</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
         </is>
       </c>
       <c r="L29" t="inlineStr" s="2">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="K30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、监控项目用例模板</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
         </is>
       </c>
       <c r="L30" t="inlineStr" s="2">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="K31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、UI设计图</t>
+          <t xml:space="preserve">来源：prd、UI图</t>
         </is>
       </c>
       <c r="L31" t="inlineStr" s="2">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="K32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、监控项目用例模板</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
         </is>
       </c>
       <c r="L32" t="inlineStr" s="2">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="K33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、监控项目用例模板</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
         </is>
       </c>
       <c r="L33" t="inlineStr" s="2">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="K34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、UI设计图</t>
+          <t xml:space="preserve">来源：prd、UI图</t>
         </is>
       </c>
       <c r="L34" t="inlineStr" s="2">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="K35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、UI设计图</t>
+          <t xml:space="preserve">来源：prd、UI图</t>
         </is>
       </c>
       <c r="L35" t="inlineStr" s="2">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="K36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、UI设计图、coverage_dimension_rules.md-分析图标题</t>
+          <t xml:space="preserve">来源：prd、UI图、coverage_dimension_rules.md-分析图标题</t>
         </is>
       </c>
       <c r="L36" t="inlineStr" s="2">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="K37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L37" t="inlineStr" s="2">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="K38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L38" t="inlineStr" s="2">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="K39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L39" t="inlineStr" s="2">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="K41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、监控项目用例模板</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
         </is>
       </c>
       <c r="L41" t="inlineStr" s="2">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="K42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、监控项目用例模板</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
         </is>
       </c>
       <c r="L42" t="inlineStr" s="2">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="K43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L43" t="inlineStr" s="2">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="K44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、监控项目用例模板</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
         </is>
       </c>
       <c r="L44" t="inlineStr" s="2">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="K45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、监控项目用例模板</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
         </is>
       </c>
       <c r="L45" t="inlineStr" s="2">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="K46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、监控项目用例模板</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
         </is>
       </c>
       <c r="L46" t="inlineStr" s="2">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、监控项目用例模板</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
         </is>
       </c>
       <c r="L47" t="inlineStr" s="2">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="K48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L48" t="inlineStr" s="2">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="K49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L49" t="inlineStr" s="2">
@@ -4390,7 +4390,7 @@
       </c>
       <c r="K50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L50" t="inlineStr" s="2">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="K51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档</t>
+          <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
       <c r="L51" t="inlineStr" s="2">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="K52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、监控项目用例模板</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
         </is>
       </c>
       <c r="L52" t="inlineStr" s="2">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="K53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、监控项目用例模板</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
         </is>
       </c>
       <c r="L53" t="inlineStr" s="2">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="K54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、监控项目用例模板</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
         </is>
       </c>
       <c r="L54" t="inlineStr" s="2">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="K55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、一键分析核心流程、监控项目用例模板</t>
+          <t xml:space="preserve">来源：prd、one_click_analysis_flow.md、monitoring_items_box_plot.md</t>
         </is>
       </c>
       <c r="L55" t="inlineStr" s="2">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="K56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：一键分析核心流程、监控项目用例模板</t>
+          <t xml:space="preserve">来源：one_click_analysis_flow.md、monitoring_items_box_plot.md</t>
         </is>
       </c>
       <c r="L56" t="inlineStr" s="2">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="K57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：一键分析核心流程、监控项目用例模板</t>
+          <t xml:space="preserve">来源：one_click_analysis_flow.md、monitoring_items_box_plot.md</t>
         </is>
       </c>
       <c r="L57" t="inlineStr" s="2">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="K58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：一键分析核心流程、监控项目用例模板</t>
+          <t xml:space="preserve">来源：one_click_analysis_flow.md、monitoring_items_box_plot.md</t>
         </is>
       </c>
       <c r="L58" t="inlineStr" s="2">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="K59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、监控项目用例模板、一键分析核心流程、数据分析核心流程</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
         </is>
       </c>
       <c r="L59" t="inlineStr" s="2">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="K60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、监控项目用例模板、一键分析核心流程、数据分析核心流程</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
         </is>
       </c>
       <c r="L60" t="inlineStr" s="2">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="K61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、监控项目用例模板、一键分析核心流程、数据分析核心流程</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
         </is>
       </c>
       <c r="L61" t="inlineStr" s="2">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="K62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、监控项目用例模板、一键分析核心流程</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md、one_click_analysis_flow.md</t>
         </is>
       </c>
       <c r="L62" t="inlineStr" s="2">
@@ -5502,25 +5502,25 @@
       <c r="H63" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 已登录业务站点并具备监控项目数据分析权限
-2. 存在当前数据源能匹配纵轴变量和样本量字段但尚未手动分析的 P控制图</t>
+2. 存在当前数据源能匹配纵轴变量和横轴变量但尚未手动分析的 P控制图</t>
         </is>
       </c>
       <c r="I63" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入业务站点 - 监控项目模块
 2. 打开目标监控项目的数据分析详情页，确认 P控制图为未分析状态且变量已匹配
-3. 执行数据替换或数据处理操作后仍能匹配字段
+3. 执行数据替换或数据处理操作后仍能匹配纵轴变量和横轴变量
 4. 确认一键分析</t>
         </is>
       </c>
       <c r="J63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P控制图一键分析成功并更新为已分析状态，配置区继续显示匹配到的纵轴变量和子组大小字段，分析结果按新数据生成</t>
+          <t xml:space="preserve">P控制图一键分析成功，分析图表、过程数据、判异检查和超出参考线检查显示正确</t>
         </is>
       </c>
       <c r="K63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、监控项目用例模板、一键分析核心流程</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md、one_click_analysis_flow.md</t>
         </is>
       </c>
       <c r="L63" t="inlineStr" s="2">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="K64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：需求文档、监控项目用例模板、一键分析核心流程</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md、one_click_analysis_flow.md</t>
         </is>
       </c>
       <c r="L64" t="inlineStr" s="2">
@@ -5648,37 +5648,123 @@
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">未分析的图参与一键分析</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">未分析的 P控制图横轴变量缺失，一键分析仍保持未分析</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P0</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">反例</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 已登录业务站点并具备监控项目数据分析权限
+2. 存在因横轴变量未配置而处于未分析状态的 P控制图</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 进入业务站点 - 监控项目模块
+2. 打开目标监控项目的数据分析详情页，确认 P控制图为未分析状态且横轴变量缺失
+3. 执行数据替换或数据处理操作
+4. 确认一键分析</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P控制图仍保持未分析状态，提示横轴变量缺失，配置区横轴变量保持为空</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md、one_click_analysis_flow.md；说明：用户确认横轴变量缺失需单独覆盖</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">困难</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="64" customHeight="1">
+      <c r="A66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">监控项目</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">一键分析</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">定类变量暂不支持分析</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr" s="2">
+      <c r="D66" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">纵轴变量为定类变量，替换数据源触发一键分析时异常提示</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr" s="2">
+      <c r="E66" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">P0</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr" s="2">
+      <c r="F66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">反例</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr" s="2">
+      <c r="H66" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 已登录业务站点并具备监控项目数据分析权限
 2. 已有分析完成的 P控制图和其他分析图
 3. 存在替换后会使纵轴变量为非数值或全空分析列的数据源</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr" s="2">
+      <c r="I66" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入业务站点 - 监控项目模块
 2. 点击已分析 P控制图监控项目的数据分析进入分析详情页
@@ -5686,7 +5772,7 @@
 4. 确认一键分析</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr" s="2">
+      <c r="J66" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">一. 分析图生成区域：
 1. P控制图分析结果状态为未分析，纵轴变量显示 -
@@ -5694,81 +5780,81 @@
 二. 配置中纵轴变量清空，不显示 NULL</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：需求文档、监控项目用例模板、一键分析核心流程</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr" s="2">
+      <c r="K66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md、one_click_analysis_flow.md</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">困难</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="64" customHeight="1">
-      <c r="A66" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">监控项目</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr" s="2">
+      <c r="M66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="64" customHeight="1">
+      <c r="A67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">监控项目</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">一键分析</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr" s="2">
+      <c r="C67" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">其他原因</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr" s="2">
+      <c r="D67" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">纵轴变量不包含整数，替换数据源触发一键分析时异常提示</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr" s="2">
+      <c r="E67" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">P0</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr" s="2">
+      <c r="F67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">反例</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr" s="2">
+      <c r="H67" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 已登录业务站点并具备监控项目数据分析权限
 2. 已有分析完成的 P控制图和其他分析图
 3. 存在替换后会使纵轴变量包含小数、负数或时分秒格式的数据源</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr" s="2">
+      <c r="I67" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入业务站点 - 监控项目模块
 2. 点击已分析 P控制图监控项目的数据分析进入分析详情页
@@ -5776,7 +5862,7 @@
 4. 确认一键分析</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr" s="2">
+      <c r="J67" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">一. 分析图生成区域：
 1. P控制图分析结果状态为未分析，纵轴变量显示正确
@@ -5784,80 +5870,80 @@
 二. 配置中纵轴变量显示正确，未生成有效分析结果</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：需求文档、监控项目用例模板、一键分析核心流程</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr" s="2">
+      <c r="K67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md、one_click_analysis_flow.md</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">困难</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="64" customHeight="1">
-      <c r="A67" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">监控项目</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr" s="2">
+      <c r="M67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="64" customHeight="1">
+      <c r="A68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">监控项目</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">一键分析</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr" s="2">
+      <c r="C68" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">其他原因</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr" s="2">
+      <c r="D68" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">样本数量小于最大计数，数据处理触发一键分析时异常提示</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr" s="2">
+      <c r="E68" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">P0</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr" s="2">
+      <c r="F68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">反例</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr" s="2">
+      <c r="H68" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 已登录业务站点并具备监控项目数据分析权限
 2. 已有分析完成的 P控制图和其他分析图</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr" s="2">
+      <c r="I68" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入业务站点 - 监控项目模块
 2. 点击已分析 P控制图监控项目的数据分析进入分析详情页
@@ -5865,7 +5951,7 @@
 4. 确认一键分析</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr" s="2">
+      <c r="J68" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">一. 分析图生成区域：
 1. P控制图分析结果状态为未分析，纵轴变量和子组大小字段显示正确
@@ -5873,295 +5959,295 @@
 二. 配置中保留当前字段，未生成有效分析结果</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：需求文档、监控项目用例模板、一键分析核心流程</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr" s="2">
+      <c r="K68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md、one_click_analysis_flow.md</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">困难</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="64" customHeight="1">
-      <c r="A68" t="inlineStr" s="2">
+      <c r="M68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="64" customHeight="1">
+      <c r="A69" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">相关性分析</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr" s="2">
+      <c r="B69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">相关性分析处创建监控项目，可选择 P控制图</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr" s="2">
+      <c r="E69" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">P0</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr" s="2">
+      <c r="F69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">联动</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr" s="2">
+      <c r="H69" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 已登录业务站点并具备相关性分析和监控项目创建权限
 2. 相关性分析列表存在已分析的记录</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr" s="2">
+      <c r="I69" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入业务站点 - 相关性分析列表
 2. 选择一条已分析记录
 3. 点击创建监控项目，添加 P控制图，点击确定</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr" s="2">
+      <c r="J69" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">监控项目列表新增对应记录，监控项目名称、监控项目类型、分析方法 P控制图、分析状态未分析显示正确</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：需求文档</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr" s="2">
+      <c r="K69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：prd</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">简单</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="64" customHeight="1">
-      <c r="A69" t="inlineStr" s="2">
+      <c r="M69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="64" customHeight="1">
+      <c r="A70" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">数据分析工作台</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr" s="2">
+      <c r="B70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">每分析一次 P控制图，分析图生成区域新增一条结果</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr" s="2">
+      <c r="E70" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">P0</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr" s="2">
+      <c r="F70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">正例</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr" s="2">
+      <c r="H70" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 已登录业务站点并具备数据分析工作台权限
 2. 存在可进入的数据分析详情页</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr" s="2">
+      <c r="I70" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入业务站点 - 数据分析工作台
 2. 进入数据分析详情页
 3. 选择 P控制图进行分析</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr" s="2">
+      <c r="J70" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">分析图生成区域新增一条 P控制图结果，显示已分析，分析结果名正确，纵轴变量、横轴变量和子组大小显示正确</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：需求文档、数据分析核心流程</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr" s="2">
+      <c r="K70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：prd、data_analysis_flow.md</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">简单</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="64" customHeight="1">
-      <c r="A70" t="inlineStr" s="2">
+      <c r="M70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="64" customHeight="1">
+      <c r="A71" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">数据分析工作台</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr" s="2">
+      <c r="B71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">存在 P控制图，正常一键分析校验</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr" s="2">
+      <c r="E71" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">P0</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr" s="2">
+      <c r="F71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">联动</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr" s="2">
+      <c r="H71" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 已登录业务站点并具备数据分析工作台权限
 2. 存在可进入的数据分析详情页
 3. 已有分析完成的 P控制图</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr" s="2">
+      <c r="I71" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入业务站点 - 数据分析工作台
 2. 进入数据分析详情页
 3. 替换数据源或执行数据处理操作</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr" s="2">
+      <c r="J71" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. P控制图一键分析成功，分析图表、过程数据、判异检查和超出参考线检查显示正确，自定义结论为空
 2. 带出 P控制图的配置项正确</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：需求文档、数据分析核心流程、一键分析核心流程</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr" s="2">
+      <c r="K71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：prd、data_analysis_flow.md、one_click_analysis_flow.md</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">困难</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr" s="2">
+      <c r="M71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P70"/>
+  <autoFilter ref="A1:P71"/>
 </worksheet>
 </file>
--- a/.claude/skills/testcase-generator/outputs/excel_exports/business_site/data_analysis_p_control_chart_testcases.xlsx
+++ b/.claude/skills/testcase-generator/outputs/excel_exports/business_site/data_analysis_p_control_chart_testcases.xlsx
@@ -324,7 +324,7 @@
       </c>
       <c r="K3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot_template.md</t>
         </is>
       </c>
       <c r="L3" t="inlineStr" s="2">
@@ -756,7 +756,7 @@
       </c>
       <c r="K8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot_template.md</t>
         </is>
       </c>
       <c r="L8" t="inlineStr" s="2">
@@ -842,7 +842,7 @@
       </c>
       <c r="K9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot_template.md</t>
         </is>
       </c>
       <c r="L9" t="inlineStr" s="2">
@@ -928,7 +928,7 @@
       </c>
       <c r="K10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot_template.md</t>
         </is>
       </c>
       <c r="L10" t="inlineStr" s="2">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="K11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot_template.md</t>
         </is>
       </c>
       <c r="L11" t="inlineStr" s="2">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="K12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot_template.md</t>
         </is>
       </c>
       <c r="L12" t="inlineStr" s="2">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="K25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot_template.md</t>
         </is>
       </c>
       <c r="L25" t="inlineStr" s="2">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="K27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot_template.md</t>
         </is>
       </c>
       <c r="L27" t="inlineStr" s="2">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="K28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot_template.md</t>
         </is>
       </c>
       <c r="L28" t="inlineStr" s="2">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="K29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot_template.md</t>
         </is>
       </c>
       <c r="L29" t="inlineStr" s="2">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="K30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot_template.md</t>
         </is>
       </c>
       <c r="L30" t="inlineStr" s="2">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="K32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot_template.md</t>
         </is>
       </c>
       <c r="L32" t="inlineStr" s="2">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="K33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot_template.md</t>
         </is>
       </c>
       <c r="L33" t="inlineStr" s="2">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="K41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot_template.md</t>
         </is>
       </c>
       <c r="L41" t="inlineStr" s="2">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="K42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot_template.md</t>
         </is>
       </c>
       <c r="L42" t="inlineStr" s="2">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="K44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot_template.md</t>
         </is>
       </c>
       <c r="L44" t="inlineStr" s="2">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="K45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot_template.md</t>
         </is>
       </c>
       <c r="L45" t="inlineStr" s="2">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="K46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot_template.md</t>
         </is>
       </c>
       <c r="L46" t="inlineStr" s="2">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="K47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot_template.md</t>
         </is>
       </c>
       <c r="L47" t="inlineStr" s="2">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="K52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot_template.md</t>
         </is>
       </c>
       <c r="L52" t="inlineStr" s="2">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="K53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot_template.md</t>
         </is>
       </c>
       <c r="L53" t="inlineStr" s="2">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="K54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot_template.md</t>
         </is>
       </c>
       <c r="L54" t="inlineStr" s="2">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="K55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、one_click_analysis_flow.md、monitoring_items_box_plot.md</t>
+          <t xml:space="preserve">来源：prd、one_click_analysis_flow.md、monitoring_items_box_plot_template.md</t>
         </is>
       </c>
       <c r="L55" t="inlineStr" s="2">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="K56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：one_click_analysis_flow.md、monitoring_items_box_plot.md</t>
+          <t xml:space="preserve">来源：one_click_analysis_flow.md、monitoring_items_box_plot_template.md</t>
         </is>
       </c>
       <c r="L56" t="inlineStr" s="2">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="K57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：one_click_analysis_flow.md、monitoring_items_box_plot.md</t>
+          <t xml:space="preserve">来源：one_click_analysis_flow.md、monitoring_items_box_plot_template.md</t>
         </is>
       </c>
       <c r="L57" t="inlineStr" s="2">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="K58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：one_click_analysis_flow.md、monitoring_items_box_plot.md</t>
+          <t xml:space="preserve">来源：one_click_analysis_flow.md、monitoring_items_box_plot_template.md</t>
         </is>
       </c>
       <c r="L58" t="inlineStr" s="2">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="K59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot_template.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
         </is>
       </c>
       <c r="L59" t="inlineStr" s="2">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="K60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot_template.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
         </is>
       </c>
       <c r="L60" t="inlineStr" s="2">
@@ -5347,7 +5347,7 @@
       </c>
       <c r="K61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot_template.md、one_click_analysis_flow.md、data_analysis_flow.md</t>
         </is>
       </c>
       <c r="L61" t="inlineStr" s="2">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="K62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md、one_click_analysis_flow.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot_template.md、one_click_analysis_flow.md</t>
         </is>
       </c>
       <c r="L62" t="inlineStr" s="2">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="K63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md、one_click_analysis_flow.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot_template.md、one_click_analysis_flow.md</t>
         </is>
       </c>
       <c r="L63" t="inlineStr" s="2">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="K64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md、one_click_analysis_flow.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot_template.md、one_click_analysis_flow.md</t>
         </is>
       </c>
       <c r="L64" t="inlineStr" s="2">
@@ -5692,7 +5692,7 @@
       </c>
       <c r="K65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md、one_click_analysis_flow.md；说明：用户确认横轴变量缺失需单独覆盖</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot_template.md、one_click_analysis_flow.md；说明：用户确认横轴变量缺失需单独覆盖</t>
         </is>
       </c>
       <c r="L65" t="inlineStr" s="2">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="K66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md、one_click_analysis_flow.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot_template.md、one_click_analysis_flow.md</t>
         </is>
       </c>
       <c r="L66" t="inlineStr" s="2">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="K67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md、one_click_analysis_flow.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot_template.md、one_click_analysis_flow.md</t>
         </is>
       </c>
       <c r="L67" t="inlineStr" s="2">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="K68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd、monitoring_items_box_plot.md、one_click_analysis_flow.md</t>
+          <t xml:space="preserve">来源：prd、monitoring_items_box_plot_template.md、one_click_analysis_flow.md</t>
         </is>
       </c>
       <c r="L68" t="inlineStr" s="2">

--- a/.claude/skills/testcase-generator/outputs/excel_exports/business_site/data_analysis_p_control_chart_testcases.xlsx
+++ b/.claude/skills/testcase-generator/outputs/excel_exports/business_site/data_analysis_p_control_chart_testcases.xlsx
@@ -269,7 +269,7 @@
     <row r="3" ht="64" customHeight="1">
       <c r="A3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B3" t="inlineStr" s="2">
@@ -329,7 +329,7 @@
       </c>
       <c r="L3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M3" t="inlineStr" s="2">
@@ -356,7 +356,7 @@
     <row r="4" ht="64" customHeight="1">
       <c r="A4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B4" t="inlineStr" s="2">
@@ -414,7 +414,7 @@
       </c>
       <c r="L4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M4" t="inlineStr" s="2">
@@ -441,7 +441,7 @@
     <row r="5" ht="64" customHeight="1">
       <c r="A5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B5" t="inlineStr" s="2">
@@ -526,17 +526,17 @@
     <row r="6" ht="64" customHeight="1">
       <c r="A6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D6" t="inlineStr" s="2">
@@ -616,17 +616,17 @@
     <row r="7" ht="64" customHeight="1">
       <c r="A7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D7" t="inlineStr" s="2">
@@ -675,7 +675,7 @@
       </c>
       <c r="L7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M7" t="inlineStr" s="2">
@@ -702,17 +702,17 @@
     <row r="8" ht="64" customHeight="1">
       <c r="A8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D8" t="inlineStr" s="2">
@@ -761,7 +761,7 @@
       </c>
       <c r="L8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M8" t="inlineStr" s="2">
@@ -788,17 +788,17 @@
     <row r="9" ht="64" customHeight="1">
       <c r="A9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D9" t="inlineStr" s="2">
@@ -874,17 +874,17 @@
     <row r="10" ht="64" customHeight="1">
       <c r="A10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D10" t="inlineStr" s="2">
@@ -933,7 +933,7 @@
       </c>
       <c r="L10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M10" t="inlineStr" s="2">
@@ -960,17 +960,17 @@
     <row r="11" ht="64" customHeight="1">
       <c r="A11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D11" t="inlineStr" s="2">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="L11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M11" t="inlineStr" s="2">
@@ -1047,17 +1047,17 @@
     <row r="12" ht="64" customHeight="1">
       <c r="A12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D12" t="inlineStr" s="2">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="L12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M12" t="inlineStr" s="2">
@@ -1134,17 +1134,17 @@
     <row r="13" ht="64" customHeight="1">
       <c r="A13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D13" t="inlineStr" s="2">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="L13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M13" t="inlineStr" s="2">
@@ -1220,17 +1220,17 @@
     <row r="14" ht="64" customHeight="1">
       <c r="A14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D14" t="inlineStr" s="2">
@@ -1306,17 +1306,17 @@
     <row r="15" ht="64" customHeight="1">
       <c r="A15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D15" t="inlineStr" s="2">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="L15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M15" t="inlineStr" s="2">
@@ -1391,17 +1391,17 @@
     <row r="16" ht="64" customHeight="1">
       <c r="A16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D16" t="inlineStr" s="2">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M16" t="inlineStr" s="2">
@@ -1477,17 +1477,17 @@
     <row r="17" ht="64" customHeight="1">
       <c r="A17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D17" t="inlineStr" s="2">
@@ -1564,17 +1564,17 @@
     <row r="18" ht="64" customHeight="1">
       <c r="A18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D18" t="inlineStr" s="2">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="L18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M18" t="inlineStr" s="2">
@@ -1650,17 +1650,17 @@
     <row r="19" ht="64" customHeight="1">
       <c r="A19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D19" t="inlineStr" s="2">
@@ -1736,17 +1736,17 @@
     <row r="20" ht="64" customHeight="1">
       <c r="A20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D20" t="inlineStr" s="2">
@@ -1822,17 +1822,17 @@
     <row r="21" ht="64" customHeight="1">
       <c r="A21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="2">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="L21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M21" t="inlineStr" s="2">
@@ -1908,17 +1908,17 @@
     <row r="22" ht="64" customHeight="1">
       <c r="A22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="2">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="L22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M22" t="inlineStr" s="2">
@@ -1994,17 +1994,17 @@
     <row r="23" ht="64" customHeight="1">
       <c r="A23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D23" t="inlineStr" s="2">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="L23" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M23" t="inlineStr" s="2">
@@ -2080,17 +2080,17 @@
     <row r="24" ht="64" customHeight="1">
       <c r="A24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D24" t="inlineStr" s="2">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="L24" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M24" t="inlineStr" s="2">
@@ -2167,17 +2167,17 @@
     <row r="25" ht="64" customHeight="1">
       <c r="A25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">配置项</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D25" t="inlineStr" s="2">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="L25" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M25" t="inlineStr" s="2">
@@ -2252,12 +2252,12 @@
     <row r="26" ht="64" customHeight="1">
       <c r="A26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B26" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C26" t="inlineStr" s="2">
@@ -2344,17 +2344,17 @@
     <row r="27" ht="64" customHeight="1">
       <c r="A27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C27" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析结果</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D27" t="inlineStr" s="2">
@@ -2428,17 +2428,17 @@
     <row r="28" ht="64" customHeight="1">
       <c r="A28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析结果</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D28" t="inlineStr" s="2">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="L28" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M28" t="inlineStr" s="2">
@@ -2515,17 +2515,17 @@
     <row r="29" ht="64" customHeight="1">
       <c r="A29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析结果</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D29" t="inlineStr" s="2">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="L29" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M29" t="inlineStr" s="2">
@@ -2602,17 +2602,17 @@
     <row r="30" ht="64" customHeight="1">
       <c r="A30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C30" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析结果</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D30" t="inlineStr" s="2">
@@ -2687,17 +2687,17 @@
     <row r="31" ht="64" customHeight="1">
       <c r="A31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C31" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析结果</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D31" t="inlineStr" s="2">
@@ -2776,12 +2776,12 @@
     <row r="32" ht="64" customHeight="1">
       <c r="A32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C32" t="inlineStr" s="2">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="L32" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M32" t="inlineStr" s="2">
@@ -2865,12 +2865,12 @@
     <row r="33" ht="64" customHeight="1">
       <c r="A33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B33" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C33" t="inlineStr" s="2">
@@ -2951,12 +2951,12 @@
     <row r="34" ht="64" customHeight="1">
       <c r="A34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B34" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C34" t="inlineStr" s="2">
@@ -3038,17 +3038,17 @@
     <row r="35" ht="64" customHeight="1">
       <c r="A35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C35" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">过程数据校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D35" t="inlineStr" s="2">
@@ -3124,12 +3124,12 @@
     <row r="36" ht="64" customHeight="1">
       <c r="A36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C36" t="inlineStr" s="2">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="L36" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M36" t="inlineStr" s="2">
@@ -3210,17 +3210,17 @@
     <row r="37" ht="64" customHeight="1">
       <c r="A37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析图校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D37" t="inlineStr" s="2">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="L37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M37" t="inlineStr" s="2">
@@ -3295,17 +3295,17 @@
     <row r="38" ht="64" customHeight="1">
       <c r="A38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析图校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D38" t="inlineStr" s="2">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="L38" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M38" t="inlineStr" s="2">
@@ -3380,17 +3380,17 @@
     <row r="39" ht="64" customHeight="1">
       <c r="A39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C39" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析图校验</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D39" t="inlineStr" s="2">
@@ -3465,12 +3465,12 @@
     <row r="40" ht="64" customHeight="1">
       <c r="A40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C40" t="inlineStr" s="2">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="L40" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一般</t>
+          <t xml:space="preserve">困难</t>
         </is>
       </c>
       <c r="M40" t="inlineStr" s="2">
@@ -3555,12 +3555,12 @@
     <row r="41" ht="64" customHeight="1">
       <c r="A41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B41" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C41" t="inlineStr" s="2">
@@ -3642,17 +3642,17 @@
     <row r="42" ht="64" customHeight="1">
       <c r="A42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C42" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析不同数据类型</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D42" t="inlineStr" s="2">
@@ -3729,17 +3729,17 @@
     <row r="43" ht="64" customHeight="1">
       <c r="A43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C43" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析不同数据类型</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D43" t="inlineStr" s="2">
@@ -3816,12 +3816,12 @@
     <row r="44" ht="64" customHeight="1">
       <c r="A44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B44" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C44" t="inlineStr" s="2">
@@ -3902,17 +3902,17 @@
     <row r="45" ht="64" customHeight="1">
       <c r="A45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C45" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">自定义结论</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D45" t="inlineStr" s="2">
@@ -3989,17 +3989,17 @@
     <row r="46" ht="64" customHeight="1">
       <c r="A46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C46" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">自定义结论</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D46" t="inlineStr" s="2">
@@ -4075,17 +4075,17 @@
     <row r="47" ht="64" customHeight="1">
       <c r="A47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C47" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">自定义结论</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D47" t="inlineStr" s="2">
@@ -4161,12 +4161,12 @@
     <row r="48" ht="64" customHeight="1">
       <c r="A48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B48" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C48" t="inlineStr" s="2">
@@ -4248,17 +4248,17 @@
     <row r="49" ht="64" customHeight="1">
       <c r="A49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C49" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">异常情况</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D49" t="inlineStr" s="2">
@@ -4335,17 +4335,17 @@
     <row r="50" ht="64" customHeight="1">
       <c r="A50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">异常情况</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D50" t="inlineStr" s="2">
@@ -4422,17 +4422,17 @@
     <row r="51" ht="64" customHeight="1">
       <c r="A51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C51" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">异常情况</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D51" t="inlineStr" s="2">
@@ -4509,17 +4509,17 @@
     <row r="52" ht="64" customHeight="1">
       <c r="A52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C52" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">异常情况</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D52" t="inlineStr" s="2">
@@ -4596,7 +4596,7 @@
     <row r="53" ht="64" customHeight="1">
       <c r="A53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B53" t="inlineStr" s="2">
@@ -4657,7 +4657,7 @@
       </c>
       <c r="L53" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">困难</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M53" t="inlineStr" s="2">
@@ -4684,17 +4684,17 @@
     <row r="54" ht="64" customHeight="1">
       <c r="A54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">更改配置</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C54" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">更改配置后分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D54" t="inlineStr" s="2">
@@ -4769,7 +4769,7 @@
     <row r="55" ht="64" customHeight="1">
       <c r="A55" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B55" t="inlineStr" s="2">
@@ -4856,12 +4856,12 @@
     <row r="56" ht="64" customHeight="1">
       <c r="A56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B56" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C56" t="inlineStr" s="2">
@@ -4942,17 +4942,17 @@
     <row r="57" ht="64" customHeight="1">
       <c r="A57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C57" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析结果提示</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D57" t="inlineStr" s="2">
@@ -5028,17 +5028,17 @@
     <row r="58" ht="64" customHeight="1">
       <c r="A58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C58" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析结果提示</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D58" t="inlineStr" s="2">
@@ -5115,12 +5115,12 @@
     <row r="59" ht="64" customHeight="1">
       <c r="A59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B59" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C59" t="inlineStr" s="2">
@@ -5203,17 +5203,17 @@
     <row r="60" ht="64" customHeight="1">
       <c r="A60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C60" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据替换</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D60" t="inlineStr" s="2">
@@ -5292,12 +5292,12 @@
     <row r="61" ht="64" customHeight="1">
       <c r="A61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B61" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C61" t="inlineStr" s="2">
@@ -5379,12 +5379,12 @@
     <row r="62" ht="64" customHeight="1">
       <c r="A62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B62" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C62" t="inlineStr" s="2">
@@ -5466,17 +5466,17 @@
     <row r="63" ht="64" customHeight="1">
       <c r="A63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C63" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">未分析的图参与一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D63" t="inlineStr" s="2">
@@ -5552,17 +5552,17 @@
     <row r="64" ht="64" customHeight="1">
       <c r="A64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">未分析的图参与一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D64" t="inlineStr" s="2">
@@ -5638,17 +5638,17 @@
     <row r="65" ht="64" customHeight="1">
       <c r="A65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">未分析的图参与一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D65" t="inlineStr" s="2">
@@ -5724,12 +5724,12 @@
     <row r="66" ht="64" customHeight="1">
       <c r="A66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C66" t="inlineStr" s="2">
@@ -5814,12 +5814,12 @@
     <row r="67" ht="64" customHeight="1">
       <c r="A67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B67" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C67" t="inlineStr" s="2">
@@ -5904,17 +5904,17 @@
     <row r="68" ht="64" customHeight="1">
       <c r="A68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">监控项目</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">一键分析</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="C68" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">其他原因</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="D68" t="inlineStr" s="2">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="L69" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M69" t="inlineStr" s="2">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="L70" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">简单</t>
+          <t xml:space="preserve">一般</t>
         </is>
       </c>
       <c r="M70" t="inlineStr" s="2">
@@ -6163,7 +6163,7 @@
     <row r="71" ht="64" customHeight="1">
       <c r="A71" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">数据分析工作台</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="B71" t="inlineStr" s="2">

--- a/.claude/skills/testcase-generator/outputs/excel_exports/business_site/data_analysis_p_control_chart_testcases.xlsx
+++ b/.claude/skills/testcase-generator/outputs/excel_exports/business_site/data_analysis_p_control_chart_testcases.xlsx
@@ -219,7 +219,7 @@
         <is>
           <t xml:space="preserve">1. 已登录业务站点并具备监控项目查看、数据分析权限
 2. 系统已存在分析方法为 P控制图且数据满足分析条件的监控项目
-3. 数据源包含缺陷数、样本量和批次数据</t>
+3. 数据源包含不合格品个数、样本量和批次数据</t>
         </is>
       </c>
       <c r="I2" t="inlineStr" s="2">
@@ -657,7 +657,7 @@
         <is>
           <t xml:space="preserve">1. 已登录业务站点并具备监控项目数据分析权限
 2. 系统已存在分析方法为 P控制图的监控项目
-3. 变量列表中存在可用于缺陷数的整数定量变量</t>
+3. 变量列表中存在可用于不合格品个数的整数定量变量</t>
         </is>
       </c>
       <c r="I7" t="inlineStr" s="2">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="D18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">纵轴缺陷数大于子组数量时阻止分析</t>
+          <t xml:space="preserve">纵轴不合格品个数大于子组数量时阻止分析</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
@@ -1604,14 +1604,14 @@
         <is>
           <t xml:space="preserve">1. 已登录业务站点并具备监控项目数据分析权限
 2. 系统已存在分析方法为 P控制图的监控项目
-3. 数据源中存在缺陷数大于子组数量的数据</t>
+3. 数据源中存在不合格品个数大于子组数量的数据</t>
         </is>
       </c>
       <c r="I18" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入业务站点 - 监控项目模块
 2. 点击目标监控项目的数据分析进入分析详情页
-3. 配置纵轴变量和小于最大缺陷数的子组大小
+3. 配置纵轴变量和小于最大不合格品个数的子组大小
 4. 点击开始分析</t>
         </is>
       </c>
@@ -1961,7 +1961,7 @@
       </c>
       <c r="J22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">参考线新增成功，列表显示全选、类型、名称、范围、数值、操作列，新增参考线信息与输入一致</t>
+          <t xml:space="preserve">参考线新增成功，列表显示全选、类型、名称、范围、数值、操作列，新增参考线信息与输入一致；P控制图仅允许添加具体数据的参考线</t>
         </is>
       </c>
       <c r="K22" t="inlineStr" s="2">
@@ -2565,7 +2565,7 @@
         <is>
           <t xml:space="preserve">1. 左侧分析流程展示数据源、算法配置、分析结果，数据源文件名以超链接展示
 2. 详细结论区域展示 P控制图图表、过程数据、超出警戒线检查、判异检查结果和输入结论
-3. 分析图标题显示缺陷数的 P 控制图，纵轴为比率，横轴为批次号或样本顺序
+3. 分析图标题显示不合格品率的 P 控制图，纵轴为比率，横轴为批次号或样本顺序
 4. 图表包含数据点、UCL、P均值和 LCL 标签，异常点以红色数值或标记突出展示
 5. 参考线和判异结果区域的颜色、链接、字号、对齐和换行样式与 UI 图一致</t>
         </is>
@@ -3154,7 +3154,7 @@
         <is>
           <t xml:space="preserve">1. 已登录业务站点并具备监控项目数据分析权限
 2. 系统已存在分析方法为 P控制图的监控项目
-3. 已准备可与 Minitab 对比的缺陷数和样本量数据</t>
+3. 已准备可与 Minitab 对比的不合格品个数和样本量数据</t>
         </is>
       </c>
       <c r="I36" t="inlineStr" s="2">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="J37" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">分析图标题显示为纵轴变量_P控制图；分析图包含横轴批次或样本序号、纵轴比率、数据点、中心线、UCL、LCL；样本量变化场景下控制限随样本量呈凹凸状</t>
+          <t xml:space="preserve">分析图标题显示为纵轴变量_P控制图；分析图包含横轴批次或样本序号、纵轴不合格品率、数据点、中心线、UCL、LCL；样本量变化场景下控制限随样本量呈凹凸状</t>
         </is>
       </c>
       <c r="K37" t="inlineStr" s="2">
@@ -3304,287 +3304,463 @@
       </c>
       <c r="D38" t="inlineStr" s="2">
         <is>
+          <t xml:space="preserve">样本量变化时控制限呈凹凸状</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P1</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">正例</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 已登录业务站点并具备监控项目数据分析权限
+2. 系统已存在分析方法为 P控制图的监控项目
+3. 数据源中不同批次样本量存在变化</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 进入业务站点 - 监控项目模块
+2. 点击目标监控项目的数据分析进入分析详情页
+3. 子组大小选择包含大小的列并选择样本量列
+4. 点击开始分析
+5. 查看 P控制图分析图和过程数据</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">分析成功；分析图中 UCL 和 LCL 随各批次样本量变化呈凹凸状，样本量小的批次控制限较宽、样本量大的批次控制限较窄；数据点按对应批次顺序展示</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：prd、UI图</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">一般</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="64" customHeight="1">
+      <c r="A39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">固定子组大小下控制限按直线展示</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">P2</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">正例</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 已登录业务站点并具备监控项目数据分析权限
+2. 系统已存在分析方法为 P控制图的监控项目
+3. 数据源包含不合格品个数和批次字段</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">1. 进入业务站点 - 监控项目模块
+2. 点击目标监控项目的数据分析进入分析详情页
+3. 子组大小选择数字并输入固定样本量
+4. 点击开始分析
+5. 查看 P控制图分析图</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">分析成功；控制限按固定子组大小生成，同一批次序列中 UCL、LCL 和中心线展示为水平直线，不受不存在的样本量列影响</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">来源：prd</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">一般</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="64" customHeight="1">
+      <c r="A40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr" s="2">
+        <is>
           <t xml:space="preserve">判异检查结果显示正确</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr" s="2">
+      <c r="E40" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr" s="2">
+      <c r="F40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">正例</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr" s="2">
+      <c r="H40" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 已登录业务站点并具备监控项目数据分析权限
 2. 系统已存在已完成且触发判异规则的 P控制图分析结果</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr" s="2">
+      <c r="I40" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入业务站点 - 监控项目模块
 2. 点击已分析 P控制图监控项目的数据分析进入分析详情页
 3. 查看判异检查区域和分析图标记</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr" s="2">
+      <c r="J40" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">判异检查区域显示命中的判异规则和数据点；异常点在分析图中突出标示；数据点旁显示触发的判异项编号</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr" s="2">
+      <c r="K40" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr" s="2">
+      <c r="L40" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">困难</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="64" customHeight="1">
-      <c r="A39" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr" s="2">
+      <c r="M40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="64" customHeight="1">
+      <c r="A41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">超出参考线检查结果显示正确</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr" s="2">
+      <c r="E41" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr" s="2">
+      <c r="F41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">正例</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr" s="2">
+      <c r="H41" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 已登录业务站点并具备监控项目数据分析权限
 2. 系统已存在包含参考线且存在超出参考线数据点的 P控制图分析结果</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr" s="2">
+      <c r="I41" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入业务站点 - 监控项目模块
 2. 点击已分析 P控制图监控项目的数据分析进入分析详情页
 3. 查看超出参考线检查区域和分析图标记</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr" s="2">
+      <c r="J41" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">超出参考线检查区域显示超出参考线的数据点；超出4项判异数据点显示方形标记，超出参考线数据点显示圆形标记</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr" s="2">
+      <c r="K41" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr" s="2">
+      <c r="L41" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">困难</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="64" customHeight="1">
-      <c r="A40" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr" s="2">
+      <c r="M41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="64" customHeight="1">
+      <c r="A42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">参考线名称超长时完整展示</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr" s="2">
+      <c r="E42" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr" s="2">
+      <c r="F42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">UI</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr" s="2">
+      <c r="H42" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 已登录业务站点并具备监控项目数据分析权限
 2. 系统已存在包含超长参考线名称的 P控制图分析结果</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr" s="2">
+      <c r="I42" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入业务站点 - 监控项目模块
 2. 点击已分析 P控制图监控项目的数据分析进入分析详情页
 3. 查看参考线区域</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr" s="2">
+      <c r="J42" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">参考线区域右侧固定宽度并根据参考线名称和数值长度自适应展示；超出最大宽度时换行展示，不截断、不遮挡其他内容</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr" s="2">
+      <c r="K42" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr" s="2">
+      <c r="L42" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">一般</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="64" customHeight="1">
-      <c r="A41" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr" s="2">
+      <c r="M42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="64" customHeight="1">
+      <c r="A43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">小数保留位数设置</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr" s="2">
+      <c r="D43" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">【待确认】小数位数选择5后数值展示生效</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr" s="2">
+      <c r="E43" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">P1</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr" s="2">
+      <c r="F43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">正例</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr" s="2">
+      <c r="H43" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 已登录业务站点并具备监控项目数据分析权限
 2. 系统已存在分析方法为 P控制图的监控项目
-3. 数据源包含可分析的缺陷数和样本量数据</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr" s="2">
+3. 数据源包含可分析的不合格品个数和样本量数据</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入业务站点 - 监控项目模块
 2. 点击目标监控项目的数据分析进入分析详情页
@@ -3593,86 +3769,86 @@
 5. 查看结果页涉及数值展示的区域</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr" s="2">
+      <c r="J43" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">分析成功；结果页中由小数位数配置控制的数值按5位展示；配置项中小数位数回显为5</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr" s="2">
+      <c r="K43" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">来源：prd、data_analysis_coverage_rules.md；说明：PRD 未明确小数位数具体生效字段范围，需要确认</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr" s="2">
+      <c r="L43" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">一般</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="64" customHeight="1">
-      <c r="A42" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr" s="2">
+      <c r="M43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="64" customHeight="1">
+      <c r="A44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">分析不同数据类型</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr" s="2">
+      <c r="D44" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">纵轴变量选择整数列，分析成功</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr" s="2">
+      <c r="E44" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr" s="2">
+      <c r="F44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">正例</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr" s="2">
+      <c r="H44" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 已登录业务站点并具备监控项目数据分析权限
 2. 系统已存在分析方法为 P控制图的监控项目
-3. 数据源包含可用于缺陷数的非负整数列和样本量</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr" s="2">
+3. 数据源包含可用于不合格品个数的非负整数列和样本量</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入业务站点 - 监控项目模块
 2. 点击目标监控项目的数据分析进入分析详情页
@@ -3680,86 +3856,86 @@
 4. 点击开始分析</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr" s="2">
+      <c r="J44" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">分析成功，分析图表、过程数据、判异检查和超出参考线检查显示正确</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr" s="2">
+      <c r="K44" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr" s="2">
+      <c r="L44" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">简单</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="64" customHeight="1">
-      <c r="A43" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr" s="2">
+      <c r="M44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="64" customHeight="1">
+      <c r="A45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">纵轴变量选择含0整数列，分析成功</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr" s="2">
+      <c r="E45" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr" s="2">
+      <c r="F45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">正例</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr" s="2">
+      <c r="H45" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 已登录业务站点并具备监控项目数据分析权限
 2. 系统已存在分析方法为 P控制图的监控项目
-3. 数据源包含缺陷数为0的整数列</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr" s="2">
+3. 数据源包含不合格品个数为0的整数列</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入业务站点 - 监控项目模块
 2. 点击目标监控项目的数据分析进入分析详情页
@@ -3767,86 +3943,86 @@
 4. 点击开始分析</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">分析图表、过程数据、判异检查和超出参考线检查显示正确，0 值数据点按实际缺陷数参与计算</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr" s="2">
+      <c r="J45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">分析图表、过程数据、判异检查和超出参考线检查显示正确，0 值数据点按实际不合格品个数参与计算</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr" s="2">
+      <c r="L45" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">简单</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="64" customHeight="1">
-      <c r="A44" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr" s="2">
+      <c r="M45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="64" customHeight="1">
+      <c r="A46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">异常情况</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr" s="2">
+      <c r="D46" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">纵轴变量缺失值静默排除</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr" s="2">
+      <c r="E46" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr" s="2">
+      <c r="F46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">正例</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr" s="2">
+      <c r="H46" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 已登录业务站点并具备监控项目数据分析权限
 2. 系统已存在分析方法为 P控制图的监控项目
 3. 数据源中纵轴变量存在部分空白或非数值</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr" s="2">
+      <c r="I46" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入业务站点 - 监控项目模块
 2. 点击目标监控项目的数据分析进入分析详情页
@@ -3854,86 +4030,86 @@
 4. 点击开始分析</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr" s="2">
+      <c r="J46" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">无提示，系统静默处理并自动排除纵轴变量缺失数据，仅使用有效数值计算，分析结果显示正确</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr" s="2">
+      <c r="K46" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr" s="2">
+      <c r="L46" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">简单</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O44" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="64" customHeight="1">
-      <c r="A45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr" s="2">
+      <c r="M46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="64" customHeight="1">
+      <c r="A47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">纵轴变量不包含整数时阻止分析</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr" s="2">
+      <c r="E47" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr" s="2">
+      <c r="F47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">反例</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr" s="2">
+      <c r="H47" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 已登录业务站点并具备监控项目数据分析权限
 2. 系统已存在分析方法为 P控制图的监控项目
 3. 纵轴变量下存在小数、负数或时分秒格式数据</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr" s="2">
+      <c r="I47" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入业务站点 - 监控项目模块
 2. 点击目标监控项目的数据分析进入分析详情页
@@ -3941,86 +4117,86 @@
 4. 点击开始分析</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr" s="2">
+      <c r="J47" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">阻止分析，提示：纵轴变量未包含整数，暂不支持分析；不生成 P控制图分析结果</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr" s="2">
+      <c r="K47" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr" s="2">
+      <c r="L47" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">一般</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="64" customHeight="1">
-      <c r="A46" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr" s="2">
+      <c r="M47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="64" customHeight="1">
+      <c r="A48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">横轴变量缺失值显示星号</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr" s="2">
+      <c r="E48" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr" s="2">
+      <c r="F48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">正例</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr" s="2">
+      <c r="H48" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 已登录业务站点并具备监控项目数据分析权限
 2. 系统已存在分析方法为 P控制图的监控项目
 3. 横轴变量下存在部分缺失值</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr" s="2">
+      <c r="I48" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入业务站点 - 监控项目模块
 2. 点击目标监控项目的数据分析进入分析详情页
@@ -4028,86 +4204,86 @@
 4. 点击开始分析</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr" s="2">
+      <c r="J48" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">无提示，系统静默处理；分析图中横轴对应缺失值的位置显示为星号，不跳过该位置</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr" s="2">
+      <c r="K48" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr" s="2">
+      <c r="L48" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">一般</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="64" customHeight="1">
-      <c r="A47" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr" s="2">
+      <c r="M48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="64" customHeight="1">
+      <c r="A49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">没有足够的数据时阻止分析</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr" s="2">
+      <c r="E49" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr" s="2">
+      <c r="F49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">反例</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr" s="2">
+      <c r="H49" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 已登录业务站点并具备监控项目数据分析权限
 2. 系统已存在分析方法为 P控制图的监控项目
 3. 分析列中只有一个有效数据或没有有效数据</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr" s="2">
+      <c r="I49" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入业务站点 - 监控项目模块
 2. 点击目标监控项目的数据分析进入分析详情页
@@ -4115,86 +4291,86 @@
 4. 点击开始分析</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr" s="2">
+      <c r="J49" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">阻止分析，提示：没有足够的数据，暂不支持分析</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr" s="2">
+      <c r="K49" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">来源：prd</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr" s="2">
+      <c r="L49" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">简单</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="64" customHeight="1">
-      <c r="A48" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr" s="2">
+      <c r="M49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="64" customHeight="1">
+      <c r="A50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">【待确认】UCL大于1或LCL小于0时静默处理</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr" s="2">
+      <c r="E50" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">P2</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr" s="2">
+      <c r="F50" t="inlineStr" s="2">
+        <is>
+          <t xml:space="preserve">AI Agent</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">边界</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr" s="2">
+      <c r="H50" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 已登录业务站点并具备监控项目数据分析权限
 2. 系统已存在分析方法为 P控制图的监控项目
 3. 数据源中存在会导致 UCL 大于1或 LCL 小于0的极端数据</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr" s="2">
+      <c r="I50" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入业务站点 - 监控项目模块
 2. 点击目标监控项目的数据分析进入分析详情页
@@ -4202,190 +4378,14 @@
 4. 查看分析图和过程数据中的 UCL、LCL</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr" s="2">
+      <c r="J50" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">系统不拦截分析；UCL 大于1时按1展示或参与展示，LCL 小于0时按0展示或参与展示，分析结果不出现越界控制限</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：prd；说明：极值处理优先按 Minitab 对比或产品确认口径判定，无法对比时再由需求补充公式说明</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">一般</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="64" customHeight="1">
-      <c r="A49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">分析图校验</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">样本量变化时控制限呈凹凸状</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">正例</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 已登录业务站点并具备监控项目数据分析权限
-2. 系统已存在分析方法为 P控制图的监控项目
-3. 数据源中不同批次样本量存在变化</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 进入业务站点 - 监控项目模块
-2. 点击目标监控项目的数据分析进入分析详情页
-3. 子组大小选择包含大小的列并选择样本量列
-4. 点击开始分析
-5. 查看 P控制图分析图</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">分析成功；分析图中 UCL 和 LCL 随各批次样本量变化呈凹凸状，数据点按对应批次顺序展示</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">来源：prd、UI图</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">一般</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="64" customHeight="1">
-      <c r="A50" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">数字子组大小下控制限按固定样本量展示</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">P2</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">AI Agent</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">正例</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 已登录业务站点并具备监控项目数据分析权限
-2. 系统已存在分析方法为 P控制图的监控项目
-3. 数据源包含缺陷数和批次字段</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">1. 进入业务站点 - 监控项目模块
-2. 点击目标监控项目的数据分析进入分析详情页
-3. 子组大小选择数字并输入固定样本量
-4. 点击开始分析
-5. 查看 P控制图分析图</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr" s="2">
-        <is>
-          <t xml:space="preserve">分析成功；控制限按固定子组大小生成，同一批次序列中 UCL、LCL 和中心线展示稳定，不受不存在的样本量列影响</t>
-        </is>
-      </c>
       <c r="K50" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">来源：prd</t>
+          <t xml:space="preserve">来源：prd；说明：极值处理优先按 Minitab 对比或产品确认口径判定，过程数据控制限数值展示口径需要确认</t>
         </is>
       </c>
       <c r="L50" t="inlineStr" s="2">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="J64" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P控制图由未分析变为已分析，分析图表、过程数据、判异检查和超出参考线检查按修复后的数据生成，未分析标签和悬浮原因被清除</t>
+          <t xml:space="preserve">P控制图由未分析变为已分析，分析图表、过程数据、判异检查、超出参考线检查按修复后的数据生成，未分析标签和悬浮原因被清除</t>
         </is>
       </c>
       <c r="K64" t="inlineStr" s="2">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="D65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">未分析的 P控制图缺陷数与子组数量关系修复后一键分析成功</t>
+          <t xml:space="preserve">未分析的 P控制图不合格品个数与子组数量关系修复后一键分析成功</t>
         </is>
       </c>
       <c r="E65" t="inlineStr" s="2">
@@ -5660,21 +5660,21 @@
       <c r="H65" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 已登录业务站点并具备监控项目数据分析权限
-2. 系统已存在因缺陷数大于子组数量处于未分析状态的 P控制图
-3. 已准备可修正缺陷数或子组数量的数据处理操作</t>
+2. 系统已存在因不合格品个数大于子组数量处于未分析状态的 P控制图
+3. 已准备可修正不合格品个数或子组数量的数据处理操作</t>
         </is>
       </c>
       <c r="I65" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">1. 进入业务站点 - 监控项目模块
 2. 打开目标监控项目的数据分析详情页，确认 P控制图为未分析状态且提示样本数量至少必须和最大计数一样大
-3. 通过数据处理修正缺陷数或子组数量，使每行缺陷数不大于子组数量
+3. 通过数据处理修正不合格品个数或子组数量，使每行不合格品个数不大于子组数量
 4. 返回数据分析并确认一键分析</t>
         </is>
       </c>
       <c r="J65" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P控制图由未分析变为已分析；分析图表、过程数据、判异检查和超出参考线检查按修复后的缺陷数和子组大小重新生成，未分析原因被清除</t>
+          <t xml:space="preserve">P控制图由未分析变为已分析；分析图表、过程数据、判异检查和超出参考线检查按修复后的不合格品个数和子组大小重新生成，未分析原因被清除</t>
         </is>
       </c>
       <c r="K65" t="inlineStr" s="2">
@@ -5755,13 +5755,13 @@
         <is>
           <t xml:space="preserve">1. 进入业务站点 - 监控项目模块
 2. 打开目标监控项目的数据分析详情页，确认 P控制图为未分析状态且提示纵轴变量未包含整数，暂不支持分析
-3. 通过数据处理修正纵轴变量数据，使其仅包含合法整数缺陷数
+3. 通过数据处理修正纵轴变量数据，使其仅包含合法整数不合格品个数
 4. 返回数据分析并确认一键分析</t>
         </is>
       </c>
       <c r="J66" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P控制图由未分析变为已分析；纵轴变量仍按原字段参与分析；分析图表、过程数据、判异检查和超出参考线检查按修复后的整数缺陷数重新生成，未分析原因被清除</t>
+          <t xml:space="preserve">P控制图由未分析变为已分析；纵轴变量仍按原字段参与分析；分析图表、过程数据、判异检查和超出参考线检查按修复后的整数不合格品个数重新生成，未分析原因被清除</t>
         </is>
       </c>
       <c r="K66" t="inlineStr" s="2">
@@ -6274,7 +6274,7 @@
         <is>
           <t xml:space="preserve">1. 进入业务站点 - 监控项目模块
 2. 点击已分析 P控制图监控项目的数据分析进入分析详情页
-3. 执行数据处理操作后返回数据分析，使缺陷数大于子组数量
+3. 执行数据处理操作后返回数据分析，使不合格品个数大于子组数量
 4. 确认一键分析</t>
         </is>
       </c>
@@ -6439,7 +6439,7 @@
         <is>
           <t xml:space="preserve">1. 已登录业务站点并具备数据分析工作台权限
 2. 系统已存在可进入的数据分析详情页
-3. 数据源包含缺陷数、样本量和批次字段</t>
+3. 数据源包含不合格品个数、样本量和批次字段</t>
         </is>
       </c>
       <c r="I74" t="inlineStr" s="2">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="J75" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">P控制图一键分析成功，分析图表、过程数据、判异检查和超出参考线检查显示正确，输入结论为空；带出 P控制图的配置项正确</t>
+          <t xml:space="preserve">P控制图一键分析成功，分析图表、过程数据、判异检查、超出参考线检查显示正确，输入结论为空；带出 P控制图的配置项正确</t>
         </is>
       </c>
       <c r="K75" t="inlineStr" s="2">
